--- a/IPO_Rawdata_master.xlsx
+++ b/IPO_Rawdata_master.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,13 +30,24 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -51,8 +62,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -101827,101 +101841,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>연번</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>상장일</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>업체</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>시장구분</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>발행금액</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>인수회사</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>인수금액</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>인수수수료</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>청약수수료 추정</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>수수료합계</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>건수</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>주관형태</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>상장트랙</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>기관배정수량</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>공모가</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>인수비율</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>총기관배정수량</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>청약일</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>납입일</t>
         </is>
@@ -101961,10 +101975,10 @@
         <v>3.6</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -101980,6 +101994,9 @@
         <is>
           <t>스팩</t>
         </is>
+      </c>
+      <c r="N2" t="n">
+        <v>4500000</v>
       </c>
       <c r="O2" t="n">
         <v>2000</v>
@@ -101992,7 +102009,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-12~01-13</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -102032,13 +102049,13 @@
         <v>375</v>
       </c>
       <c r="H3" t="n">
-        <v>9.99785</v>
+        <v>9.997999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8125</v>
+        <v>2.812</v>
       </c>
       <c r="J3" t="n">
-        <v>12.81035</v>
+        <v>12.81</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -102054,6 +102071,9 @@
         <is>
           <t>이익실현</t>
         </is>
+      </c>
+      <c r="N3" t="n">
+        <v>2812500</v>
       </c>
       <c r="O3" t="n">
         <v>10000</v>
@@ -102066,7 +102086,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-20~01-21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -102081,38 +102101,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>케이뱅크</t>
+          <t>덕양에너젠</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>유가증권</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4980</v>
+        <v>750</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2490</v>
+        <v>375</v>
       </c>
       <c r="H4" t="n">
-        <v>30.39875</v>
+        <v>9.997999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>16.1178032</v>
+        <v>2.812</v>
       </c>
       <c r="J4" t="n">
-        <v>46.5165532</v>
+        <v>12.81</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -102129,23 +102149,26 @@
           <t>이익실현</t>
         </is>
       </c>
+      <c r="N4" t="n">
+        <v>2812500</v>
+      </c>
       <c r="O4" t="n">
-        <v>8300</v>
+        <v>10000</v>
       </c>
       <c r="P4" t="n">
         <v>0.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>38838080</v>
+        <v>5625000</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-20~01-21</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-23</t>
         </is>
       </c>
     </row>
@@ -102155,38 +102178,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>에스팀</t>
+          <t>케이뱅크</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가증권</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>153</v>
+        <v>4980</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>153</v>
+        <v>2490</v>
       </c>
       <c r="H5" t="n">
-        <v>7.8795</v>
+        <v>30.399</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1475</v>
+        <v>16.118</v>
       </c>
       <c r="J5" t="n">
-        <v>9.027000000000001</v>
+        <v>46.517</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -102203,23 +102226,26 @@
           <t>이익실현</t>
         </is>
       </c>
+      <c r="N5" t="n">
+        <v>22500000</v>
+      </c>
       <c r="O5" t="n">
-        <v>8500</v>
+        <v>8300</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1350000</v>
+        <v>45000000</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-20~23</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
@@ -102229,38 +102255,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>액스비스</t>
+          <t>케이뱅크</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가증권</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>264.5</v>
+        <v>4980</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>264.5</v>
+        <v>2290.8</v>
       </c>
       <c r="H6" t="n">
-        <v>10.8974</v>
+        <v>27.967</v>
       </c>
       <c r="I6" t="n">
-        <v>1.98375</v>
+        <v>14.828</v>
       </c>
       <c r="J6" t="n">
-        <v>12.88115</v>
+        <v>42.795</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -102277,23 +102303,26 @@
           <t>이익실현</t>
         </is>
       </c>
+      <c r="N6" t="n">
+        <v>20700000</v>
+      </c>
       <c r="O6" t="n">
-        <v>11500</v>
+        <v>8300</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>1725000</v>
+        <v>45000000</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-20~23</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
@@ -102303,71 +102332,70 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>카나프테라퓨틱스</t>
+          <t>케이뱅크</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가증권</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>4980</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>199.2</v>
       </c>
       <c r="H7" t="n">
-        <v>20.5</v>
+        <v>1.394</v>
       </c>
       <c r="I7" t="n">
-        <v>2.936</v>
+        <v>1.289</v>
       </c>
       <c r="J7" t="n">
-        <v>23.436</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+        <v>2.683</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>대표</t>
+          <t>인수</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>혁신기술</t>
-        </is>
+          <t>이익실현</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1800000</v>
       </c>
       <c r="O7" t="n">
-        <v>20000</v>
+        <v>8300</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1468000</v>
+        <v>45000000</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-20~23</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
@@ -102377,12 +102405,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>아이엠바이오로직스</t>
+          <t>에스팀</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -102391,7 +102419,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>520</v>
+        <v>153</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -102399,16 +102427,16 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>364</v>
+        <v>153</v>
       </c>
       <c r="H8" t="n">
-        <v>19.8399992</v>
+        <v>7.88</v>
       </c>
       <c r="I8" t="n">
-        <v>2.73</v>
+        <v>1.147</v>
       </c>
       <c r="J8" t="n">
-        <v>22.5699992</v>
+        <v>9.026999999999999</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -102422,26 +102450,29 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>혁신기술</t>
-        </is>
+          <t>이익실현</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1350000</v>
       </c>
       <c r="O8" t="n">
-        <v>26000</v>
+        <v>8500</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1500000</v>
+        <v>1350000</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-23~02-24</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-26</t>
         </is>
       </c>
     </row>
@@ -102451,12 +102482,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>한패스</t>
+          <t>액스비스</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -102465,24 +102496,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>209</v>
+        <v>264.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>167.2</v>
+        <v>264.5</v>
       </c>
       <c r="H9" t="n">
-        <v>6.02756</v>
+        <v>10.897</v>
       </c>
       <c r="I9" t="n">
-        <v>1.254</v>
+        <v>1.984</v>
       </c>
       <c r="J9" t="n">
-        <v>7.281560000000001</v>
+        <v>12.881</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -102499,23 +102530,26 @@
           <t>이익실현</t>
         </is>
       </c>
+      <c r="N9" t="n">
+        <v>1725000</v>
+      </c>
       <c r="O9" t="n">
-        <v>19000</v>
+        <v>11500</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7999999999999999</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>825000</v>
+        <v>1725000</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-23~02-24</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
     </row>
@@ -102525,12 +102559,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>카나프테라퓨틱스</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -102539,24 +102573,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>290.52</v>
+        <v>400</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>290.52</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>14.96178</v>
+        <v>20.5</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1789</v>
+        <v>2.936</v>
       </c>
       <c r="J10" t="n">
-        <v>17.14068</v>
+        <v>23.436</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -102573,23 +102607,26 @@
           <t>혁신기술</t>
         </is>
       </c>
+      <c r="N10" t="n">
+        <v>1500000</v>
+      </c>
       <c r="O10" t="n">
-        <v>21600</v>
+        <v>20000</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1008750</v>
+        <v>1500000</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-05~03-06</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -102599,12 +102636,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NH스팩33호</t>
+          <t>아이엠바이오로직스</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -102613,24 +102650,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>127</v>
+        <v>520</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>127</v>
+        <v>364</v>
       </c>
       <c r="H11" t="n">
-        <v>3.81</v>
+        <v>19.84</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9525</v>
+        <v>2.73</v>
       </c>
       <c r="J11" t="n">
-        <v>4.7625</v>
+        <v>22.57</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -102644,26 +102681,29 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>스팩</t>
-        </is>
+          <t>혁신기술</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>1050000</v>
       </c>
       <c r="O11" t="n">
-        <v>2000</v>
+        <v>26000</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>4762500</v>
+        <v>1500000</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-11~03-12</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -102673,12 +102713,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>리센스메디컬</t>
+          <t>아이엠바이오로직스</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -102687,33 +102727,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>154</v>
+        <v>520</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="H12" t="n">
-        <v>6.08</v>
+        <v>6.66</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5775</v>
+        <v>1.17</v>
       </c>
       <c r="J12" t="n">
-        <v>6.6575</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+        <v>7.83</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>대표</t>
+          <t>공동</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -102721,23 +102757,26 @@
           <t>혁신기술</t>
         </is>
       </c>
+      <c r="N12" t="n">
+        <v>450000</v>
+      </c>
       <c r="O12" t="n">
-        <v>11000</v>
+        <v>26000</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1050000</v>
+        <v>1500000</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-11~03-12</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -102747,12 +102786,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>신한스팩17호</t>
+          <t>한패스</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -102761,24 +102800,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>100</v>
+        <v>167.2</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5</v>
+        <v>6.028</v>
       </c>
       <c r="I13" t="n">
-        <v>0.75</v>
+        <v>1.254</v>
       </c>
       <c r="J13" t="n">
-        <v>4.25</v>
+        <v>7.282</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -102792,26 +102831,29 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>스팩</t>
-        </is>
+          <t>이익실현</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>660000</v>
       </c>
       <c r="O13" t="n">
-        <v>2000</v>
+        <v>19000</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>3750000</v>
+        <v>825000</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>2026-03-16~03-17</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
           <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
         </is>
       </c>
     </row>
@@ -102821,12 +102863,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>교보스팩20호</t>
+          <t>한패스</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -102835,57 +102877,56 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>108</v>
+        <v>209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>108</v>
+        <v>41.8</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>1.507</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.314</v>
       </c>
       <c r="J14" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+        <v>1.821</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>대표</t>
+          <t>공동</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>스팩</t>
-        </is>
+          <t>이익실현</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>165000</v>
       </c>
       <c r="O14" t="n">
-        <v>2000</v>
+        <v>19000</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4050000</v>
+        <v>825000</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-16~03-17</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-19</t>
         </is>
       </c>
     </row>
@@ -102895,12 +102936,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>인벤테라</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -102909,24 +102950,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>195.88</v>
+        <v>290.52</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>137.116</v>
+        <v>290.52</v>
       </c>
       <c r="H15" t="n">
-        <v>7.06</v>
+        <v>14.962</v>
       </c>
       <c r="I15" t="n">
-        <v>0.95865</v>
+        <v>2.179</v>
       </c>
       <c r="J15" t="n">
-        <v>8.018649999999999</v>
+        <v>17.141</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -102940,26 +102981,29 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>기술성 평가</t>
-        </is>
+          <t>혁신기술</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>1008750</v>
       </c>
       <c r="O15" t="n">
-        <v>16600</v>
+        <v>21600</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7000000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>825000</v>
+        <v>1008750</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-16~03-17</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-19</t>
         </is>
       </c>
     </row>
@@ -102969,12 +103013,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>키움히어로스팩2호</t>
+          <t>NH스팩33호</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -102983,24 +103027,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>3.81</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9</v>
+        <v>3.81</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -103016,6 +103060,9 @@
         <is>
           <t>스팩</t>
         </is>
+      </c>
+      <c r="N16" t="n">
+        <v>4762500</v>
       </c>
       <c r="O16" t="n">
         <v>2000</v>
@@ -103024,16 +103071,16 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>4500000</v>
+        <v>4762500</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-17~03-18</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
     </row>
@@ -103043,12 +103090,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>채비</t>
+          <t>리센스메디컬</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -103057,7 +103104,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1107</v>
+        <v>154</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -103065,16 +103112,16 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>415.125</v>
+        <v>77</v>
       </c>
       <c r="H17" t="n">
-        <v>12.690786375</v>
+        <v>6.08</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1134375</v>
+        <v>0.578</v>
       </c>
       <c r="J17" t="n">
-        <v>15.804223875</v>
+        <v>6.658</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -103083,31 +103130,34 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>공동대표</t>
+          <t>대표</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>이익미실현</t>
-        </is>
+          <t>혁신기술</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>525000</v>
       </c>
       <c r="O17" t="n">
-        <v>12300</v>
+        <v>11000</v>
       </c>
       <c r="P17" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>6750000</v>
+        <v>1050000</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-19~03-20</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
     </row>
@@ -103117,12 +103167,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>신한스팩18호</t>
+          <t>리센스메디컬</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -103131,24 +103181,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>154</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="I18" t="n">
-        <v>0.75</v>
+        <v>0.578</v>
       </c>
       <c r="J18" t="n">
-        <v>4.25</v>
+        <v>3.658</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -103162,26 +103212,29 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>스팩</t>
-        </is>
+          <t>혁신기술</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>525000</v>
       </c>
       <c r="O18" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>3750000</v>
+        <v>1050000</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-19~03-20</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
     </row>
@@ -103191,12 +103244,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>코스모로보틱스</t>
+          <t>신한스팩17호</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -103205,24 +103258,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>250.2</v>
+        <v>100</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>118.845</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>6.80544</v>
+        <v>3.5</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8282955</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>7.6337355</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -103231,31 +103284,34 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>공동대표</t>
+          <t>대표</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>기술성 평가</t>
-        </is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>3750000</v>
       </c>
       <c r="O19" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="P19" t="n">
-        <v>0.475</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2906300</v>
+        <v>3750000</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-19~03-20</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
     </row>
@@ -103265,12 +103321,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>폴레드</t>
+          <t>교보스팩20호</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -103279,24 +103335,24 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="H20" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>0.975</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>6.375</v>
+        <v>3</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -103310,26 +103366,29 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>이익실현</t>
-        </is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4050000</v>
       </c>
       <c r="O20" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1950000</v>
+        <v>4050000</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-03-23~03-24</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -103339,12 +103398,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>마키나락스</t>
+          <t>인벤테라</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -103353,24 +103412,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>395.25</v>
+        <v>195.88</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>335.9625</v>
+        <v>137.116</v>
       </c>
       <c r="H21" t="n">
-        <v>19.076745</v>
+        <v>7.06</v>
       </c>
       <c r="I21" t="n">
-        <v>2.07436125</v>
+        <v>0.959</v>
       </c>
       <c r="J21" t="n">
-        <v>21.15110625</v>
+        <v>8.019</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -103387,23 +103446,26 @@
           <t>기술성 평가</t>
         </is>
       </c>
+      <c r="N21" t="n">
+        <v>619500</v>
+      </c>
       <c r="O21" t="n">
-        <v>15000</v>
+        <v>16600</v>
       </c>
       <c r="P21" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>1626950</v>
+        <v>885000</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-23~03-24</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -103413,12 +103475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>대신밸런스스팩20호</t>
+          <t>인벤테라</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -103427,57 +103489,56 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>130</v>
+        <v>195.88</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>130</v>
+        <v>58.764</v>
       </c>
       <c r="H22" t="n">
-        <v>3.9</v>
+        <v>5.04</v>
       </c>
       <c r="I22" t="n">
-        <v>0.975</v>
+        <v>0.411</v>
       </c>
       <c r="J22" t="n">
-        <v>4.875</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+        <v>5.451</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>대표</t>
+          <t>공동</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>스팩</t>
-        </is>
+          <t>기술성 평가</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>265500</v>
       </c>
       <c r="O22" t="n">
-        <v>2000</v>
+        <v>16600</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>4875000</v>
+        <v>885000</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-03-23~03-24</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -103487,12 +103548,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>피스피스스튜디오</t>
+          <t>키움히어로스팩2호</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -103501,24 +103562,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>488.616955</v>
+        <v>120</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>244.308585</v>
+        <v>120</v>
       </c>
       <c r="H23" t="n">
-        <v>9.972345010000002</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>1.832313581249645</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>11.80465859124965</v>
+        <v>3</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -103527,31 +103588,30 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>공동대표</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>이익실현</t>
-        </is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>4500000</v>
       </c>
       <c r="O23" t="n">
-        <v>21500</v>
+        <v>2000</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5000002200087387</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1704477</v>
+        <v>4500000</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-14~04-15</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -103561,12 +103621,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
+          <t>채비</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -103575,24 +103635,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>140</v>
+        <v>1107</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>메리츠</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>140</v>
+        <v>415.125</v>
       </c>
       <c r="H24" t="n">
-        <v>2.45</v>
+        <v>12.691</v>
       </c>
       <c r="I24" t="n">
-        <v>1.05</v>
+        <v>3.113</v>
       </c>
       <c r="J24" t="n">
-        <v>3.5</v>
+        <v>15.804</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -103601,31 +103661,34 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>대표</t>
+          <t>공동대표</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>스팩</t>
-        </is>
+          <t>이익미실현</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2531250</v>
       </c>
       <c r="O24" t="n">
-        <v>2000</v>
+        <v>12300</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>0.375</v>
       </c>
       <c r="Q24" t="n">
-        <v>5250000</v>
+        <v>6750000</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-20~04-21</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -103635,12 +103698,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>져스텍</t>
+          <t>채비</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -103649,7 +103712,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>200</v>
+        <v>1107</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -103657,16 +103720,16 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>200</v>
+        <v>415.125</v>
       </c>
       <c r="H25" t="n">
-        <v>11.639</v>
+        <v>12.691</v>
       </c>
       <c r="I25" t="n">
-        <v>1.45</v>
+        <v>3.113</v>
       </c>
       <c r="J25" t="n">
-        <v>13.089</v>
+        <v>15.804</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -103675,31 +103738,34 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>대표</t>
+          <t>공동대표</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>기술성 평가</t>
-        </is>
+          <t>이익미실현</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>2531250</v>
       </c>
       <c r="O25" t="n">
-        <v>12500</v>
+        <v>12300</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>0.375</v>
       </c>
       <c r="Q25" t="n">
-        <v>1160000</v>
+        <v>6750000</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-20~04-21</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -103709,12 +103775,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한국제16호스팩</t>
+          <t>채비</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -103723,57 +103789,56 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>110</v>
+        <v>1107</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>110</v>
+        <v>138.375</v>
       </c>
       <c r="H26" t="n">
-        <v>3.3</v>
+        <v>4.23</v>
       </c>
       <c r="I26" t="n">
-        <v>0.825</v>
+        <v>1.038</v>
       </c>
       <c r="J26" t="n">
-        <v>4.125</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+        <v>5.268</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>대표</t>
+          <t>공동</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>스팩</t>
-        </is>
+          <t>이익미실현</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>843750</v>
       </c>
       <c r="O26" t="n">
-        <v>2000</v>
+        <v>12300</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>0.125</v>
       </c>
       <c r="Q26" t="n">
-        <v>4125000</v>
+        <v>6750000</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-04-20~04-21</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -103783,249 +103848,1343 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>채비</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1107</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>하나</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>138.375</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5.268</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>공동</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>이익미실현</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>843750</v>
+      </c>
+      <c r="O27" t="n">
+        <v>12300</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>6750000</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2026-04-20~04-21</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>신한스팩18호</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>신한</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>100</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>2026-04-20~04-21</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>코스모로보틱스</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>250.2</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>유진</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>118.845</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6.805</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="J29" t="n">
+        <v>7.633</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>공동대표</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>기술성 평가</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>1485562</v>
+      </c>
+      <c r="O29" t="n">
+        <v>6000</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3127500</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>2026-04-27~04-28</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>코스모로보틱스</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>250.2</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>118.845</v>
+      </c>
+      <c r="H30" t="n">
+        <v>5.517</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6.345</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>공동대표</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>기술성 평가</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>1485562</v>
+      </c>
+      <c r="O30" t="n">
+        <v>6000</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3127500</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>2026-04-27~04-28</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>코스모로보틱스</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>250.2</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>유안타</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>인수</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>기술성 평가</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>156375</v>
+      </c>
+      <c r="O31" t="n">
+        <v>6000</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3127500</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>2026-04-27~04-28</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>폴레드</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>130</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>130</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="J32" t="n">
+        <v>6.375</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>이익실현</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>1950000</v>
+      </c>
+      <c r="O32" t="n">
+        <v>5000</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1950000</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>2026-05-04~05-05</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>마키나락스</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>395.25</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>335.962</v>
+      </c>
+      <c r="H33" t="n">
+        <v>19.077</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.074</v>
+      </c>
+      <c r="J33" t="n">
+        <v>21.151</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>기술성 평가</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>1679811</v>
+      </c>
+      <c r="O33" t="n">
+        <v>15000</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.8499989999999999</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1976250</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>2026-05-11~05-12</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>마키나락스</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>395.25</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>59.288</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.552</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>인수</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>기술성 평가</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>296439</v>
+      </c>
+      <c r="O34" t="n">
+        <v>15000</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.150001</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1976250</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>2026-05-11~05-12</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>대신밸런스스팩20호</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>130</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>대신</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>130</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>4875000</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4875000</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>2026-05-22~05-25</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>피스피스스튜디오</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>488.617</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>244.309</v>
+      </c>
+      <c r="H36" t="n">
+        <v>9.772</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.832</v>
+      </c>
+      <c r="J36" t="n">
+        <v>11.604</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>공동대표</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>이익실현</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>852241</v>
+      </c>
+      <c r="O36" t="n">
+        <v>21500</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.500001</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1704478</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>2026-05-26~05-27</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>피스피스스튜디오</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>488.617</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>244.308</v>
+      </c>
+      <c r="H37" t="n">
+        <v>9.772</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.832</v>
+      </c>
+      <c r="J37" t="n">
+        <v>11.604</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>공동대표</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>이익실현</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>852237</v>
+      </c>
+      <c r="O37" t="n">
+        <v>21500</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.499999</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1704478</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>2026-05-26~05-27</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>메리츠제2호스팩</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>140</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>메리츠</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>140</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>5250000</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>5250000</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2026-06-09~06-10</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>져스텍</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>200</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>삼성</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>200</v>
+      </c>
+      <c r="H39" t="n">
+        <v>11.639</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J39" t="n">
+        <v>13.089</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>기술성 평가</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="O39" t="n">
+        <v>12500</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2026-06-18~06-19</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>스트라드비젼</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E40" t="n">
         <v>840</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="G40" t="n">
         <v>840</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H40" t="n">
         <v>25.752</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I40" t="n">
         <v>6.3</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J40" t="n">
         <v>32.052</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>대표</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>기술성 평가</t>
         </is>
       </c>
-      <c r="O27" t="n">
+      <c r="N40" t="n">
+        <v>5250000</v>
+      </c>
+      <c r="O40" t="n">
         <v>12000</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P40" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q40" t="n">
         <v>5250000</v>
       </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2026-06-18~06-19</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한국제16호스팩</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>110</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>110</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>스팩</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>4125000</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>4125000</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2026-06-22~06-23</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>매드업</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E42" t="n">
         <v>160</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>미래</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="G42" t="n">
         <v>160</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H42" t="n">
         <v>7.416</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I42" t="n">
         <v>1.2</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J42" t="n">
         <v>8.616</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>대표</t>
         </is>
       </c>
-      <c r="O28" t="n">
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="O42" t="n">
         <v>8000</v>
       </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2026-06-23~24</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>레몬헬스케어</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E43" t="n">
         <v>200</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="G43" t="n">
         <v>200</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H43" t="n">
         <v>8.24</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I43" t="n">
         <v>1.5</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J43" t="n">
         <v>9.74</v>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>대표</t>
         </is>
       </c>
-      <c r="O29" t="n">
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="O43" t="n">
         <v>10000</v>
       </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2026-06-24~25</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>미상장(납입 7/6)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>미상장(납입완료)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>레메디</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E44" t="n">
         <v>248.4</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="G44" t="n">
         <v>248.4</v>
       </c>
-      <c r="H30" t="n">
-        <v>11.513</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="H44" t="n">
+        <v>12.793</v>
+      </c>
+      <c r="I44" t="n">
         <v>1.863</v>
       </c>
-      <c r="J30" t="n">
-        <v>13.376</v>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="J44" t="n">
+        <v>14.656</v>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>대표</t>
         </is>
       </c>
-      <c r="O30" t="n">
-        <v>20700</v>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>

--- a/IPO_Rawdata_master.xlsx
+++ b/IPO_Rawdata_master.xlsx
@@ -105177,13 +105177,23 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>900000</v>
+      </c>
+      <c r="O44" t="n">
+        <v>20700</v>
+      </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
+      <c r="Q44" t="n">
+        <v>900000</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>07-01~07-02</t>
+        </is>
+      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>2026-07-06</t>

--- a/IPO_Rawdata_master.xlsx
+++ b/IPO_Rawdata_master.xlsx
@@ -101841,7 +101841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105133,12 +105133,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>미상장(납입완료)</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -105147,7 +105147,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>248.4</v>
+        <v>551.48</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -105155,16 +105155,16 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>248.4</v>
+        <v>496.33</v>
       </c>
       <c r="H44" t="n">
-        <v>12.793</v>
+        <v>12.757</v>
       </c>
       <c r="I44" t="n">
-        <v>1.863</v>
+        <v>3.722</v>
       </c>
       <c r="J44" t="n">
-        <v>14.656</v>
+        <v>16.479</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -105178,23 +105178,165 @@
       </c>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
+        <v>1731367</v>
+      </c>
+      <c r="O44" t="n">
+        <v>21500</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.899996</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1923750</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>07-13~07-14</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>에이치엘지노믹스</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>551.48</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>IBK</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>공동주관</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="n">
+        <v>192383</v>
+      </c>
+      <c r="O45" t="n">
+        <v>21500</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.100004</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1923750</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>07-13~07-14</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>미상장(납입완료)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>레메디</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>248.4</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>248.4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>12.793</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.863</v>
+      </c>
+      <c r="J46" t="n">
+        <v>14.656</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="n">
         <v>900000</v>
       </c>
-      <c r="O44" t="n">
+      <c r="O46" t="n">
         <v>20700</v>
       </c>
-      <c r="P44" t="n">
+      <c r="P46" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q46" t="n">
         <v>900000</v>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>07-01~07-02</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>

--- a/IPO_Rawdata_master.xlsx
+++ b/IPO_Rawdata_master.xlsx
@@ -21,7 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -62,11 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -495,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1316"/>
+  <dimension ref="A1:R1317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72989,6 +72992,53 @@
         <is>
           <t>총조달 1.0% 대표주관</t>
         </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="n">
+        <v>1316</v>
+      </c>
+      <c r="B1317" s="2" t="n">
+        <v>45516</v>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>M83</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>이익실현</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>신영</t>
+        </is>
+      </c>
+      <c r="F1317" s="2" t="n">
+        <v>45520</v>
+      </c>
+      <c r="G1317" s="2" t="n">
+        <v>45526</v>
+      </c>
+      <c r="H1317" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="I1317" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J1317" t="n">
+        <v>11000</v>
+      </c>
+      <c r="K1317" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L1317" t="n">
+        <v>16000</v>
+      </c>
+      <c r="O1317" t="n">
+        <v>638.0700000000001</v>
       </c>
     </row>
   </sheetData>
@@ -101841,7 +101891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102365,7 +102415,6 @@
       <c r="J7" t="n">
         <v>2.683</v>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>인수</t>
@@ -102746,7 +102795,6 @@
       <c r="J12" t="n">
         <v>7.83</v>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>공동</t>
@@ -102896,7 +102944,6 @@
       <c r="J14" t="n">
         <v>1.821</v>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>공동</t>
@@ -103508,7 +103555,6 @@
       <c r="J22" t="n">
         <v>5.451</v>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>공동</t>
@@ -103591,7 +103637,6 @@
           <t>대표</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
         <v>4500000</v>
       </c>
@@ -103808,7 +103853,6 @@
       <c r="J26" t="n">
         <v>5.268</v>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>공동</t>
@@ -103881,7 +103925,6 @@
       <c r="J27" t="n">
         <v>5.268</v>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>공동</t>
@@ -104185,7 +104228,6 @@
       <c r="J31" t="n">
         <v>0.65</v>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>인수</t>
@@ -104412,7 +104454,6 @@
       <c r="J34" t="n">
         <v>1.552</v>
       </c>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>인수</t>
@@ -104495,7 +104536,6 @@
           <t>대표</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
         <v>4875000</v>
       </c>
@@ -105030,7 +105070,6 @@
           <t>대표</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
         <v>1500000</v>
       </c>
@@ -105103,7 +105142,6 @@
           <t>대표</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
         <v>1500000</v>
       </c>
@@ -105133,12 +105171,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>미상장(납입완료)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -105147,7 +105185,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>551.48</v>
+        <v>248.4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -105155,16 +105193,16 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>496.33</v>
+        <v>248.4</v>
       </c>
       <c r="H44" t="n">
-        <v>12.757</v>
+        <v>12.793</v>
       </c>
       <c r="I44" t="n">
-        <v>3.722</v>
+        <v>1.863</v>
       </c>
       <c r="J44" t="n">
-        <v>16.479</v>
+        <v>14.656</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -105176,167 +105214,10 @@
           <t>대표</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="n">
-        <v>1731367</v>
-      </c>
-      <c r="O44" t="n">
-        <v>21500</v>
-      </c>
       <c r="P44" t="n">
-        <v>0.899996</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1923750</v>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>07-13~07-14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S44" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>에이치엘지노믹스</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>코스닥</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>551.48</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>IBK</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>55.15</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1.417</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1.831</v>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>공동주관</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="n">
-        <v>192383</v>
-      </c>
-      <c r="O45" t="n">
-        <v>21500</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0.100004</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1923750</v>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>07-13~07-14</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>미상장(납입완료)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>레메디</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>코스닥</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>248.4</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>KB</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>248.4</v>
-      </c>
-      <c r="H46" t="n">
-        <v>12.793</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1.863</v>
-      </c>
-      <c r="J46" t="n">
-        <v>14.656</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>대표</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="n">
-        <v>900000</v>
-      </c>
-      <c r="O46" t="n">
-        <v>20700</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>900000</v>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>07-01~07-02</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
